--- a/docs/DOH_ABCD_작업표.xlsx
+++ b/docs/DOH_ABCD_작업표.xlsx
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>설계만</t>
+          <t>✅ 구현 완료(2026-07-28) — VF008</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>✅ 가능(정면, 난이도 최하) — 화면-내 수직축. ★ 우선순위 1위 권장. 각도 단위로 내면 Sportsbox Side Bend와 대조검증도 가능</t>
+          <t>✅ 구현됨 — VF008 @P1, 단위 deg(Sportsbox Side Bend 대조 가능), 정면 전용. 판정 구간 정상≥5°/주의2~5/과다0~2/심함≤0 (근거등급 B). selfcheck_metrics.py: 기하 정답 대조 오차 0.00°, up축 전두면 롤 오차만 1:1 전파</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2178,14 +2178,14 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>▶ 우선순위(효과÷난이도): ① 어깨 높이차(P1, 난이도 최하·5엣지·Sportsbox Side Bend와 대조가능)</t>
+          <t>▶ 우선순위(효과÷난이도): ①~③ 진행 상황 — ③ Hand Depth ✅구현(VF028, 2026-07-28, 판정구간은 측면 실측 대기) ·</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → ② 리드팔 플레인(7엣지, 클럽 불필요) → ③ Hand Depth(11엣지 최대, 기준선 결정 필요) → ④ 골반 틸트(범용모델 열세 예상)</t>
+          <t xml:space="preserve">   ① 어깨 높이차 ✅구현+판정구간까지(VF008, 2026-07-28) · 남은 것 → ② 리드팔 플레인(7엣지, 클럽 불필요) → ④ 골반 틸트(범용모델 열세 예상)</t>
         </is>
       </c>
     </row>
